--- a/Config/Buff.xlsx
+++ b/Config/Buff.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88404E0-84BF-4AAD-80F6-E7917AED38F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC63B563-2B01-437F-B57B-7372B9084A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21705" yWindow="15360" windowWidth="21810" windowHeight="9525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-3600" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -896,7 +896,7 @@
         <v>5</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
